--- a/saas_analysis.xlsx
+++ b/saas_analysis.xlsx
@@ -66,13 +66,13 @@
     <t xml:space="preserve">Note</t>
   </si>
   <si>
-    <t xml:space="preserve">Asana negotiated rate ($/seat/yr)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">List is $1,200/seat. Base case assumes ~17% off on a 3-yr consolidated deal.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asana list rate ($/seat/yr)</t>
+    <t xml:space="preserve">Asana negotiated rate (€/seat/yr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">List is €1,200/seat. Base case assumes ~17% off on a 3-yr consolidated deal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asana list rate (€/seat/yr)</t>
   </si>
   <si>
     <t xml:space="preserve">Derived: current Asana cost / purchased seats.</t>
@@ -111,10 +111,10 @@
     <t xml:space="preserve">Annual cost</t>
   </si>
   <si>
-    <t xml:space="preserve">List $/seat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$/active user</t>
+    <t xml:space="preserve">List €/seat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">€/active user</t>
   </si>
   <si>
     <t xml:space="preserve">Idle seats</t>
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Total</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft Planner is bundled in the existing Microsoft 365 licence — $0 incremental, out of scope.</t>
+    <t xml:space="preserve">Microsoft Planner is bundled in the existing Microsoft 365 licence — €0 incremental, out of scope.</t>
   </si>
   <si>
     <t xml:space="preserve">End state — standardise on Asana, retire Monday.com + Trello, keep Jira</t>
@@ -246,7 +246,7 @@
     <t xml:space="preserve">Optimistic</t>
   </si>
   <si>
-    <t xml:space="preserve">Range headline: $540K (conservative) to $750K (optimistic); base case $610K.</t>
+    <t xml:space="preserve">Range headline: €540K (conservative) to €750K (optimistic); base case €610K.</t>
   </si>
 </sst>
 </file>
@@ -257,7 +257,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
+    <numFmt numFmtId="167" formatCode="\€#,##0;&quot;(€&quot;#,##0\);\-"/>
   </numFmts>
   <fonts count="13">
     <font>
